--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N29_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.06531236662449</v>
+        <v>3.910613259576479</v>
       </c>
       <c r="D2" t="n">
-        <v>47.87849675354101</v>
+        <v>7.780255722450414</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
